--- a/data/trans_dic/P1432-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1432-Provincia-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,37 +688,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,99</t>
+          <t>0,27; 2,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,22</t>
+          <t>0,71; 4,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,73</t>
+          <t>0,32; 2,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,94</t>
+          <t>0,7; 4,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,82</t>
+          <t>0,55; 2,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,5</t>
+          <t>0,16; 1,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,78</t>
+          <t>0,67; 2,74</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,41</t>
+          <t>0,17; 1,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,97</t>
+          <t>0,75; 2,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,44</t>
+          <t>1,25; 4,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,14</t>
+          <t>0,22; 2,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,76</t>
+          <t>0,51; 1,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,4</t>
+          <t>0,76; 2,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,56</t>
+          <t>0,33; 1,45</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,07</t>
+          <t>0,32; 2,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,62</t>
+          <t>0,67; 3,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,64</t>
+          <t>0,63; 2,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,23; 1,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,22</t>
+          <t>0,72; 3,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,29</t>
+          <t>2,14; 6,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,38</t>
+          <t>0,24; 1,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,04</t>
+          <t>0,53; 2,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,46</t>
+          <t>1,19; 3,59</t>
         </is>
       </c>
     </row>
@@ -1123,22 +1123,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,6</t>
+          <t>0,49; 6,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 8,74</t>
+          <t>2,38; 8,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,4</t>
+          <t>1,94; 6,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1228,32 +1228,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,61</t>
+          <t>0,63; 3,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,16</t>
+          <t>0,76; 4,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,37</t>
+          <t>0,35; 3,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,28</t>
+          <t>0,38; 2,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,85</t>
+          <t>0,65; 2,81</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,16</t>
+          <t>0,3; 1,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,89</t>
+          <t>0,88; 3,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,38</t>
+          <t>0,14; 1,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,27 +1358,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,35</t>
+          <t>0,54; 2,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,84</t>
+          <t>1,38; 3,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,42</t>
+          <t>0,36; 1,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,27</t>
+          <t>0,79; 2,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,32</t>
+          <t>0,93; 2,33</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,74</t>
+          <t>1,58; 3,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,19</t>
+          <t>0,13; 1,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,25</t>
+          <t>1,65; 4,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,25</t>
+          <t>0,55; 2,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,54</t>
+          <t>0,25; 1,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,62</t>
+          <t>1,89; 3,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,36</t>
+          <t>0,46; 1,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,05</t>
+          <t>0,22; 1,04</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,51</t>
+          <t>0,8; 1,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,01</t>
+          <t>0,42; 1,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,77</t>
+          <t>0,31; 0,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,01</t>
+          <t>1,11; 1,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,12</t>
+          <t>1,23; 2,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,96</t>
+          <t>0,99; 1,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,6</t>
+          <t>1,03; 1,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,45</t>
+          <t>0,89; 1,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,26</t>
+          <t>0,78; 1,28</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 9260</t>
+          <t>0; 8807</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1871,37 +1871,37 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>799; 8776</t>
+          <t>782; 7409</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1601; 11020</t>
+          <t>1853; 12555</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>933; 7853</t>
+          <t>932; 8167</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1887; 11362</t>
+          <t>2034; 13047</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3361; 15053</t>
+          <t>2960; 14860</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>932; 8729</t>
+          <t>928; 7927</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3917; 16181</t>
+          <t>3911; 15945</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7078</t>
+          <t>0; 7020</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5711</t>
+          <t>0; 5324</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>859; 7090</t>
+          <t>861; 7012</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3954; 14943</t>
+          <t>3759; 14693</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6664; 23199</t>
+          <t>6532; 24171</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1164; 11204</t>
+          <t>1173; 11572</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5030; 17588</t>
+          <t>5039; 18338</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7849; 24628</t>
+          <t>7763; 24518</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3410; 15960</t>
+          <t>3371; 14822</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>974; 9774</t>
+          <t>1024; 9018</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2063; 12126</t>
+          <t>2239; 12293</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6482</t>
+          <t>0; 6494</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4815; 17294</t>
+          <t>4124; 16761</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 7300</t>
+          <t>0; 7396</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6912</t>
+          <t>820; 6259</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6897</t>
+          <t>0; 6504</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4888</t>
+          <t>0; 4877</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 7449</t>
+          <t>0; 6394</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2234; 12533</t>
+          <t>2805; 12345</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8245; 24356</t>
+          <t>8290; 26236</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1755; 10103</t>
+          <t>1752; 11294</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3927; 15528</t>
+          <t>4027; 16754</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9522; 26170</t>
+          <t>8981; 27189</t>
         </is>
       </c>
     </row>
@@ -2518,22 +2518,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1038; 14041</t>
+          <t>1047; 13400</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4816</t>
+          <t>0; 5658</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 7543</t>
+          <t>0; 7049</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5324; 19203</t>
+          <t>5226; 18952</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2543,17 +2543,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7391</t>
+          <t>0; 7093</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8389; 27672</t>
+          <t>8399; 26176</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4776</t>
+          <t>0; 4789</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5205</t>
+          <t>0; 6513</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4812</t>
+          <t>0; 5536</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1611; 9509</t>
+          <t>1646; 10142</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7132</t>
+          <t>0; 7106</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2056; 11579</t>
+          <t>2102; 11286</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>959; 9215</t>
+          <t>958; 9260</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>969; 9048</t>
+          <t>967; 9064</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2112; 12596</t>
+          <t>2104; 12410</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3656; 15258</t>
+          <t>3505; 15076</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1773; 13288</t>
+          <t>1858; 12256</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5122; 19183</t>
+          <t>5832; 20206</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>907; 9039</t>
+          <t>910; 8984</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>971; 9594</t>
+          <t>972; 9589</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3909; 16302</t>
+          <t>3772; 16491</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9371; 26552</t>
+          <t>9550; 27007</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4717; 17760</t>
+          <t>4542; 17321</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>11873; 30842</t>
+          <t>10729; 30201</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12001; 31320</t>
+          <t>12522; 31470</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12142; 27834</t>
+          <t>11745; 28652</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1017; 9282</t>
+          <t>1020; 8308</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 8193</t>
+          <t>0; 8858</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13613; 33269</t>
+          <t>12902; 32607</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4391; 18537</t>
+          <t>4540; 18806</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2143; 12749</t>
+          <t>2059; 12879</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28923; 55248</t>
+          <t>28907; 54971</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6606; 21735</t>
+          <t>7338; 21752</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3347; 16849</t>
+          <t>3461; 16729</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>26480; 49392</t>
+          <t>26081; 49788</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>13565; 34740</t>
+          <t>14263; 35835</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10591; 26279</t>
+          <t>10477; 27785</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38308; 68044</t>
+          <t>37609; 66395</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>43029; 75272</t>
+          <t>43559; 73835</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38462; 69353</t>
+          <t>35140; 67268</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>68992; 106354</t>
+          <t>68472; 106966</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>64090; 101372</t>
+          <t>62191; 100231</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>53794; 87626</t>
+          <t>54011; 88710</t>
         </is>
       </c>
     </row>
